--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3154,27 +3154,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109633301</v>
+        <v>137518425</v>
       </c>
       <c r="B25" t="n">
-        <v>57132</v>
+        <v>58035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3183,27 +3183,20 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>ruvande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blåbärshällorna, Ång</t>
+          <t>Lidgatu, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599201</v>
+        <v>598860</v>
       </c>
       <c r="R25" t="n">
-        <v>7033981</v>
+        <v>7033565</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3227,17 +3220,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>9 ägg i redet</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3252,27 +3250,27 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109633301</t>
+          <t>https://artportalen.se/Sighting/137518425</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127347779</v>
+        <v>109633301</v>
       </c>
       <c r="B26" t="n">
-        <v>58327</v>
+        <v>57132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3280,16 +3278,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3298,19 +3296,27 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>ruvande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Jättjärnbäcken, Jättjärnbäcken, Ång</t>
+          <t>Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599034</v>
+        <v>599201</v>
       </c>
       <c r="R26" t="n">
-        <v>7033701</v>
+        <v>7033981</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3334,22 +3340,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:42</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:42</t>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>9 ägg i redet</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3364,27 +3365,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127347779</t>
+          <t>https://artportalen.se/Sighting/109633301</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>110386096</v>
+        <v>127347779</v>
       </c>
       <c r="B27" t="n">
-        <v>99035</v>
+        <v>58327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3392,41 +3393,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Blåbärshällorna, Ång</t>
+          <t>Jättjärnbäcken, Jättjärnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599188</v>
+        <v>599034</v>
       </c>
       <c r="R27" t="n">
-        <v>7033839</v>
+        <v>7033701</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3450,12 +3447,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3464,56 +3471,55 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110386096</t>
+          <t>https://artportalen.se/Sighting/127347779</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>110386039</v>
+        <v>110386096</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>99035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3527,10 +3533,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599181</v>
+        <v>599188</v>
       </c>
       <c r="R28" t="n">
-        <v>7033995</v>
+        <v>7033839</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3588,6 +3594,113 @@
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110386096</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>110386039</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>599181</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7033995</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/110386039</t>
         </is>
@@ -3622,6 +3735,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -3157,7 +3157,7 @@
         <v>137518425</v>
       </c>
       <c r="B25" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
